--- a/smartcards.xlsx
+++ b/smartcards.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\chris\Dropbox\07 Entwicklungen\02_SmartCards\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0D2177D-FF6C-4305-BEBF-C05086113668}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6DD5AB43-5230-4B0A-9660-C43CAACE047B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" firstSheet="4" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Anleitung" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="168">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="254" uniqueCount="169">
   <si>
     <t>SmartCards – Anleitung zur xlsx-Befüllung</t>
   </si>
@@ -529,13 +529,16 @@
   </si>
   <si>
     <t>14:45-15:30</t>
+  </si>
+  <si>
+    <t>https://cdn.pixabay.com/photo/2013/11/28/12/14/horse-220453_1280.jpg</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -572,6 +575,14 @@
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="4">
@@ -618,10 +629,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -639,8 +651,10 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Link" xfId="1" builtinId="8"/>
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -1666,6 +1680,9 @@
       <c r="C6" t="s">
         <v>23</v>
       </c>
+      <c r="D6" s="9" t="s">
+        <v>168</v>
+      </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
@@ -1726,6 +1743,9 @@
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="D6" r:id="rId1" xr:uid="{DB4FDAF6-7AAC-41A3-809A-956D46DAA9A5}"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/smartcards.xlsx
+++ b/smartcards.xlsx
@@ -8,24 +8,25 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\chris\Dropbox\07 Entwicklungen\02_SmartCards\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6DD5AB43-5230-4B0A-9660-C43CAACE047B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92353B8F-F546-40CE-BB10-18D4362388C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" firstSheet="4" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Anleitung" sheetId="1" r:id="rId1"/>
-    <sheet name="Beispiel-Deck" sheetId="2" r:id="rId2"/>
-    <sheet name="Hauptstädte" sheetId="3" r:id="rId3"/>
-    <sheet name="Mathematik" sheetId="4" r:id="rId4"/>
-    <sheet name="Tiere &amp; Fakten" sheetId="5" r:id="rId5"/>
-    <sheet name="Stundenplan" sheetId="6" r:id="rId6"/>
+    <sheet name="Test" sheetId="8" r:id="rId2"/>
+    <sheet name="Beispiel-Deck" sheetId="2" r:id="rId3"/>
+    <sheet name="Hauptstädte" sheetId="3" r:id="rId4"/>
+    <sheet name="Mathematik" sheetId="4" r:id="rId5"/>
+    <sheet name="Tiere &amp; Fakten" sheetId="5" r:id="rId6"/>
+    <sheet name="Stundenplan" sheetId="6" r:id="rId7"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="254" uniqueCount="169">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="291" uniqueCount="170">
   <si>
     <t>SmartCards – Anleitung zur xlsx-Befüllung</t>
   </si>
@@ -532,6 +533,11 @@
   </si>
   <si>
     <t>https://cdn.pixabay.com/photo/2013/11/28/12/14/horse-220453_1280.jpg</t>
+  </si>
+  <si>
+    <t>Afrikanischer Elefant
+Elefant
+Maus</t>
   </si>
 </sst>
 </file>
@@ -633,7 +639,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -652,6 +658,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Link" xfId="1" builtinId="8"/>
@@ -1037,6 +1046,161 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1DD6B1B3-9810-4155-9DCF-8AE44F59AC29}">
+  <dimension ref="A1:E11"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="2" width="30" customWidth="1"/>
+    <col min="3" max="3" width="18" customWidth="1"/>
+    <col min="4" max="5" width="40" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.35">
+      <c r="A1" s="2" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2" s="3" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>117</v>
+      </c>
+      <c r="B4" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="C4" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="D4" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="E4" s="9" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>119</v>
+      </c>
+      <c r="B5" s="10" t="s">
+        <v>169</v>
+      </c>
+      <c r="C5" s="10" t="s">
+        <v>169</v>
+      </c>
+      <c r="D5" s="10" t="s">
+        <v>169</v>
+      </c>
+      <c r="E5" s="10" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>121</v>
+      </c>
+      <c r="B6" t="s">
+        <v>122</v>
+      </c>
+      <c r="C6" t="s">
+        <v>23</v>
+      </c>
+      <c r="D6" s="9" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>123</v>
+      </c>
+      <c r="B7" t="s">
+        <v>124</v>
+      </c>
+      <c r="C7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D7" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>126</v>
+      </c>
+      <c r="B8" t="s">
+        <v>127</v>
+      </c>
+      <c r="C8" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>128</v>
+      </c>
+      <c r="B9" t="s">
+        <v>129</v>
+      </c>
+      <c r="C9" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>130</v>
+      </c>
+      <c r="B10" t="s">
+        <v>131</v>
+      </c>
+      <c r="C10" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>132</v>
+      </c>
+      <c r="B11" t="s">
+        <v>133</v>
+      </c>
+      <c r="C11" t="s">
+        <v>23</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="D6" r:id="rId1" xr:uid="{E39DB4AC-1620-4408-B987-BF73449489A6}"/>
+    <hyperlink ref="B4" r:id="rId2" xr:uid="{ECC55DD1-5951-4888-AD66-74AA862CF0AF}"/>
+    <hyperlink ref="C4" r:id="rId3" xr:uid="{40A0FDC8-0EE0-4B93-B7D9-8A3EECADE080}"/>
+    <hyperlink ref="D4" r:id="rId4" xr:uid="{7FFAF40F-61E9-4DDC-BE49-D46C4E666DEB}"/>
+    <hyperlink ref="E4" r:id="rId5" xr:uid="{6D1D61ED-5306-4A6C-A5AC-76DDEE373603}"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:E7"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1131,7 +1295,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1371,7 +1535,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1611,7 +1775,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:E11"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1750,7 +1914,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>

--- a/smartcards.xlsx
+++ b/smartcards.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\chris\Dropbox\07 Entwicklungen\02_SmartCards\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92353B8F-F546-40CE-BB10-18D4362388C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4294EFFA-3DDB-487B-9FDE-E40AE0288E14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="291" uniqueCount="170">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="292" uniqueCount="170">
   <si>
     <t>SmartCards – Anleitung zur xlsx-Befüllung</t>
   </si>
@@ -1083,8 +1083,8 @@
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>117</v>
+      <c r="A4" s="9" t="s">
+        <v>168</v>
       </c>
       <c r="B4" s="9" t="s">
         <v>168</v>
@@ -1117,8 +1117,8 @@
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>121</v>
+      <c r="A6" s="9" t="s">
+        <v>168</v>
       </c>
       <c r="B6" t="s">
         <v>122</v>
@@ -1127,6 +1127,9 @@
         <v>23</v>
       </c>
       <c r="D6" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="E6" s="9" t="s">
         <v>168</v>
       </c>
     </row>
@@ -1195,6 +1198,9 @@
     <hyperlink ref="C4" r:id="rId3" xr:uid="{40A0FDC8-0EE0-4B93-B7D9-8A3EECADE080}"/>
     <hyperlink ref="D4" r:id="rId4" xr:uid="{7FFAF40F-61E9-4DDC-BE49-D46C4E666DEB}"/>
     <hyperlink ref="E4" r:id="rId5" xr:uid="{6D1D61ED-5306-4A6C-A5AC-76DDEE373603}"/>
+    <hyperlink ref="A6" r:id="rId6" xr:uid="{9359B3FF-16DC-4EF6-9058-E249731194CF}"/>
+    <hyperlink ref="E6" r:id="rId7" xr:uid="{678A2EF5-5017-4EA6-8F3F-86E1AD79312F}"/>
+    <hyperlink ref="A4" r:id="rId8" xr:uid="{D962AD97-59E4-4E83-8B7D-044FD9FC50CA}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/smartcards.xlsx
+++ b/smartcards.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\chris\Dropbox\07 Entwicklungen\02_SmartCards\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4294EFFA-3DDB-487B-9FDE-E40AE0288E14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3361BBFE-3A15-4345-9026-025BEC6EE027}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1082,15 +1082,15 @@
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A4" s="9" t="s">
-        <v>168</v>
+    <row r="4" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>117</v>
       </c>
       <c r="B4" s="9" t="s">
         <v>168</v>
       </c>
-      <c r="C4" s="9" t="s">
-        <v>168</v>
+      <c r="C4" s="10" t="s">
+        <v>169</v>
       </c>
       <c r="D4" s="9" t="s">
         <v>168</v>
@@ -1100,8 +1100,8 @@
       </c>
     </row>
     <row r="5" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>119</v>
+      <c r="A5" s="10" t="s">
+        <v>169</v>
       </c>
       <c r="B5" s="10" t="s">
         <v>169</v>
@@ -1195,12 +1195,10 @@
   <hyperlinks>
     <hyperlink ref="D6" r:id="rId1" xr:uid="{E39DB4AC-1620-4408-B987-BF73449489A6}"/>
     <hyperlink ref="B4" r:id="rId2" xr:uid="{ECC55DD1-5951-4888-AD66-74AA862CF0AF}"/>
-    <hyperlink ref="C4" r:id="rId3" xr:uid="{40A0FDC8-0EE0-4B93-B7D9-8A3EECADE080}"/>
-    <hyperlink ref="D4" r:id="rId4" xr:uid="{7FFAF40F-61E9-4DDC-BE49-D46C4E666DEB}"/>
-    <hyperlink ref="E4" r:id="rId5" xr:uid="{6D1D61ED-5306-4A6C-A5AC-76DDEE373603}"/>
-    <hyperlink ref="A6" r:id="rId6" xr:uid="{9359B3FF-16DC-4EF6-9058-E249731194CF}"/>
-    <hyperlink ref="E6" r:id="rId7" xr:uid="{678A2EF5-5017-4EA6-8F3F-86E1AD79312F}"/>
-    <hyperlink ref="A4" r:id="rId8" xr:uid="{D962AD97-59E4-4E83-8B7D-044FD9FC50CA}"/>
+    <hyperlink ref="D4" r:id="rId3" xr:uid="{7FFAF40F-61E9-4DDC-BE49-D46C4E666DEB}"/>
+    <hyperlink ref="E4" r:id="rId4" xr:uid="{6D1D61ED-5306-4A6C-A5AC-76DDEE373603}"/>
+    <hyperlink ref="E6" r:id="rId5" xr:uid="{678A2EF5-5017-4EA6-8F3F-86E1AD79312F}"/>
+    <hyperlink ref="A6" r:id="rId6" xr:uid="{1B796BD2-4578-4430-9CEF-986800E041D5}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
